--- a/Datos_Remesa_SEPA_Norma_19.xlsx
+++ b/Datos_Remesa_SEPA_Norma_19.xlsx
@@ -320,8 +320,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -329,15 +333,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -583,11 +587,14 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="10.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="10.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15.06"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="2" width="10.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -614,25 +621,25 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="4" t="n">
         <v>45658</v>
       </c>
     </row>
@@ -659,16 +666,17 @@
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13.86"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="2" width="10.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -704,104 +712,104 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="0" t="str">
+      <c r="E2" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(A2,YEAR(F2)&amp;MONTH(F2)&amp;DAY(F2))</f>
         <v>17123456T2024110</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="4" t="n">
         <v>45301</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="0" t="str">
+      <c r="H2" s="1" t="str">
         <f aca="true">_xlfn.CONCAT(A2,"ASOC",YEAR(TODAY()))</f>
         <v>17123456TASOC2026</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="0" t="str">
+      <c r="E3" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(A3,YEAR(F3)&amp;MONTH(F3)&amp;DAY(F3))</f>
         <v>17789012V2023325</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="4" t="n">
         <v>45010</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="0" t="str">
+      <c r="H3" s="1" t="str">
         <f aca="true">_xlfn.CONCAT(A3,"ASOC",YEAR(TODAY()))</f>
         <v>17789012VASOC2026</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="J3" s="0" t="s">
+      <c r="J3" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="0" t="str">
+      <c r="E4" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(A4,YEAR(F4)&amp;MONTH(F4)&amp;DAY(F4))</f>
         <v>17345678M2022812</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="4" t="n">
         <v>44785</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="0" t="str">
+      <c r="H4" s="1" t="str">
         <f aca="true">_xlfn.CONCAT(A4,"ASOC",YEAR(TODAY()))</f>
         <v>17345678MASOC2026</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="J4" s="0" t="s">
+      <c r="J4" s="1" t="s">
         <v>36</v>
       </c>
     </row>
